--- a/excel/100(n)/AVG_Sort_Dataset.xlsx
+++ b/excel/100(n)/AVG_Sort_Dataset.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>InputSize(n)</t>
   </si>
@@ -43,6 +43,21 @@
   </si>
   <si>
     <t xml:space="preserve">BubbleSort </t>
+  </si>
+  <si>
+    <t>BubbleSort (Reverse)</t>
+  </si>
+  <si>
+    <t>InsertionSort (Reverse)</t>
+  </si>
+  <si>
+    <t>SelectionSort (Reverse)</t>
+  </si>
+  <si>
+    <t>MergeSort (Reverse)</t>
+  </si>
+  <si>
+    <t>QuickSort (Reverse)</t>
   </si>
 </sst>
 </file>
@@ -361,7 +376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="21.33203125"/>
@@ -391,25 +406,55 @@
       <c r="F1" t="s" s="0">
         <v>4</v>
       </c>
+      <c r="G1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>50542.0</v>
+        <v>55490.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>33492.0</v>
-      </c>
-      <c r="D2" t="n" s="0">
-        <v>26912.0</v>
-      </c>
-      <c r="E2" t="n" s="0">
-        <v>20846.0</v>
-      </c>
-      <c r="F2" t="n" s="0">
-        <v>20054.0</v>
+        <v>38250.0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>28618.0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19296.0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23998.0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>54460.0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>34012.0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>28442.0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19782.0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>29692.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/100(n)/AVG_Sort_Dataset.xlsx
+++ b/excel/100(n)/AVG_Sort_Dataset.xlsx
@@ -427,34 +427,34 @@
         <v>100.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>55490.0</v>
+        <v>34937.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>38250.0</v>
+        <v>19496.0</v>
       </c>
       <c r="D2" t="n">
-        <v>28618.0</v>
+        <v>17548.0</v>
       </c>
       <c r="E2" t="n">
-        <v>19296.0</v>
+        <v>16358.0</v>
       </c>
       <c r="F2" t="n">
-        <v>23998.0</v>
+        <v>19562.0</v>
       </c>
       <c r="G2" t="n">
-        <v>54460.0</v>
+        <v>35304.0</v>
       </c>
       <c r="H2" t="n">
-        <v>34012.0</v>
+        <v>17345.0</v>
       </c>
       <c r="I2" t="n">
-        <v>28442.0</v>
+        <v>18696.0</v>
       </c>
       <c r="J2" t="n">
-        <v>19782.0</v>
+        <v>16561.0</v>
       </c>
       <c r="K2" t="n">
-        <v>29692.0</v>
+        <v>18240.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/100(n)/AVG_Sort_Dataset.xlsx
+++ b/excel/100(n)/AVG_Sort_Dataset.xlsx
@@ -102,19 +102,19 @@
         <v>100.0</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>65000.0</v>
+        <v>4872.9</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>3480.0</v>
+        <v>343.3</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>42340.0</v>
+        <v>4519.6</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>20930.0</v>
+        <v>8341.3</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>13650.0</v>
+        <v>7925.6</v>
       </c>
     </row>
   </sheetData>
